--- a/Result/profitability/6934.xlsx
+++ b/Result/profitability/6934.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM15"/>
+  <dimension ref="A1:AM16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,10 +1868,10 @@
         <v>-53</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.67</v>
+        <v>-1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.075</v>
+        <v>-2.06875</v>
       </c>
       <c r="N12" t="n">
         <v>-271.00375</v>
@@ -1901,10 +1901,10 @@
         <v>114.2</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3199999999999998</v>
+        <v>-0.27</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2370370370370369</v>
+        <v>0.2</v>
       </c>
       <c r="Y12" t="n">
         <v>-395.66</v>
@@ -1913,10 +1913,10 @@
         <v>4.583111317039268</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2643171806167401</v>
+        <v>-0.2863436123348018</v>
       </c>
       <c r="AC12" t="n">
         <v>-462.1</v>
@@ -1998,7 +1998,7 @@
         <v>-1.1</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.63625</v>
+        <v>-1.63</v>
       </c>
       <c r="N13" t="n">
         <v>-161.8175</v>
@@ -2028,10 +2028,10 @@
         <v>114.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5699999999999998</v>
+        <v>0.52</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.341317365269461</v>
+        <v>-0.3209876543209876</v>
       </c>
       <c r="Y13" t="n">
         <v>350.26</v>
@@ -2125,7 +2125,7 @@
         <v>0.22</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3</v>
+        <v>-1.29375</v>
       </c>
       <c r="N14" t="n">
         <v>-87.2975</v>
@@ -2252,7 +2252,7 @@
         <v>-1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9924999999999999</v>
+        <v>-0.9862500000000001</v>
       </c>
       <c r="N15" t="n">
         <v>-119.38875</v>
@@ -2333,6 +2333,133 @@
       </c>
       <c r="AM15" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6934</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>33</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-101.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-47</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-293.13%</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-45</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.8600000000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-129.6275</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1188811188811189</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>344.52</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.7719125291270837</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.3600000000000001</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.2222222222222223</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>380.19</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.7887922985954066</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
